--- a/outputs/daily/hr_rankings_2026-10-28_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28_remaining.xlsx
@@ -735,24 +735,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -765,14 +765,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q2" t="n">
         <v>41.2</v>
@@ -799,13 +799,13 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -886,72 +886,72 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr"/>
@@ -975,12 +975,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1005,14 +1005,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>53.3</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59.6</v>
+        <v>50.1</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -1039,13 +1039,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>16.6</v>
+        <v>63.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1131,67 +1131,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -1215,24 +1215,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1245,14 +1245,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1270,22 +1282,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1299,7 +1311,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1324,7 +1336,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1356,90 +1368,114 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -1455,24 +1491,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1485,14 +1521,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>47</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1506,11 +1542,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q5" t="n">
         <v>41.2</v>
@@ -1519,13 +1555,13 @@
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1539,7 +1575,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1581,12 +1617,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1596,7 +1632,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1611,67 +1647,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr"/>
@@ -1695,24 +1731,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1725,14 +1761,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1746,26 +1794,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1779,7 +1827,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1804,7 +1852,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1821,12 +1869,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1836,12 +1884,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1851,75 +1899,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -1935,24 +2007,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1965,14 +2037,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1990,7 +2062,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>41.2</v>
@@ -1999,13 +2071,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2019,7 +2091,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2061,22 +2133,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2091,67 +2163,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -2175,12 +2247,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2205,7 +2277,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2226,11 +2298,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -2239,13 +2311,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2259,7 +2331,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2301,22 +2373,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2331,67 +2403,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -2415,12 +2487,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2445,14 +2517,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.2</v>
+        <v>42.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2466,11 +2538,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
         <v>41.2</v>
@@ -2479,13 +2551,13 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>65.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2499,7 +2571,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2541,22 +2613,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2566,72 +2638,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
@@ -2655,24 +2727,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -2685,14 +2757,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>40.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2706,26 +2790,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -2739,7 +2823,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2764,7 +2848,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -2781,12 +2865,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2796,90 +2880,114 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -2928,11 +3036,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>35.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2953,7 +3073,7 @@
         <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -2962,7 +3082,7 @@
         <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -3004,7 +3124,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3041,7 +3161,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3114,12 +3234,36 @@
           <t>0.1288</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -3135,24 +3279,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3165,14 +3309,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>32.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3186,11 +3330,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -3199,13 +3343,13 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3219,7 +3363,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3244,7 +3388,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3261,22 +3405,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3291,67 +3435,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -3375,24 +3519,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3405,14 +3549,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3426,11 +3570,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -3439,13 +3583,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3459,7 +3603,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3501,12 +3645,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3516,7 +3660,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3531,67 +3675,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -3615,24 +3759,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3645,14 +3789,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3666,26 +3822,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3699,7 +3855,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3724,7 +3880,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3746,7 +3902,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3756,12 +3912,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3771,75 +3927,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -3855,12 +4035,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3885,14 +4065,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3906,26 +4098,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -3939,7 +4131,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3964,7 +4156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -3981,27 +4173,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4011,75 +4203,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4095,12 +4311,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4125,14 +4341,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4150,7 +4366,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
         <v>41.2</v>
@@ -4159,13 +4375,13 @@
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
         <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4179,7 +4395,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4221,12 +4437,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4236,7 +4452,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4251,67 +4467,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr"/>
@@ -4335,12 +4551,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4365,14 +4581,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>30.3</v>
+        <v>28.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4386,26 +4614,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4419,7 +4647,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4444,7 +4672,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4461,12 +4689,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4476,12 +4704,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4491,75 +4719,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4575,24 +4827,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4605,14 +4857,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>29.9</v>
+        <v>26.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4626,26 +4890,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4659,7 +4923,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -4684,7 +4948,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -4701,12 +4965,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4716,12 +4980,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -4731,75 +4995,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -4848,11 +5136,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4873,7 +5173,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>17.3</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -4924,7 +5224,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -4961,7 +5261,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5034,12 +5334,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5381,24 +5705,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5411,14 +5735,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5436,7 +5760,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q2" t="n">
         <v>41.2</v>
@@ -5445,13 +5769,13 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -5465,7 +5789,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -5512,17 +5836,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -5532,72 +5856,72 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr"/>
@@ -5621,12 +5945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5651,14 +5975,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>53.3</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5676,7 +6000,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59.6</v>
+        <v>50.1</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -5685,13 +6009,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>16.6</v>
+        <v>63.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -5705,7 +6029,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -5747,22 +6071,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -5777,67 +6101,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -5861,24 +6185,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5891,14 +6215,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5916,22 +6252,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -5945,7 +6281,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -5970,7 +6306,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -5987,12 +6323,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6002,90 +6338,114 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -6101,24 +6461,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6131,14 +6491,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>47</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6152,11 +6512,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q5" t="n">
         <v>41.2</v>
@@ -6165,13 +6525,13 @@
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6185,7 +6545,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6227,12 +6587,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -6242,7 +6602,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -6257,67 +6617,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr"/>
@@ -6341,24 +6701,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6371,14 +6731,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6392,26 +6764,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6425,7 +6797,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6450,7 +6822,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6467,12 +6839,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -6482,12 +6854,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6497,75 +6869,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6581,24 +6977,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6611,14 +7007,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -6636,7 +7032,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>41.2</v>
@@ -6645,13 +7041,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -6665,7 +7061,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -6707,22 +7103,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -6737,67 +7133,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -6821,12 +7217,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6851,7 +7247,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6872,11 +7268,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -6885,13 +7281,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6905,7 +7301,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -6947,22 +7343,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -6977,67 +7373,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -7061,12 +7457,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7091,14 +7487,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.2</v>
+        <v>42.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7112,11 +7508,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
         <v>41.2</v>
@@ -7125,13 +7521,13 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>65.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7145,7 +7541,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7187,22 +7583,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -7212,72 +7608,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
@@ -7301,24 +7697,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -7331,14 +7727,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>40.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7352,26 +7760,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7385,7 +7793,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -7410,7 +7818,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -7427,12 +7835,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -7442,90 +7850,114 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -7574,11 +8006,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>35.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -7599,7 +8043,7 @@
         <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -7608,7 +8052,7 @@
         <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -7650,7 +8094,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -7687,7 +8131,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -7760,12 +8204,36 @@
           <t>0.1288</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -7781,24 +8249,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -7811,14 +8279,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>32.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -7832,11 +8300,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -7845,13 +8313,13 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -7865,7 +8333,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -7890,7 +8358,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -7907,22 +8375,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -7937,67 +8405,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -8021,24 +8489,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8051,14 +8519,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8072,11 +8540,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -8085,13 +8553,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8105,7 +8573,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8147,12 +8615,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -8162,7 +8630,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -8177,67 +8645,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -8261,24 +8729,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8291,14 +8759,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8312,26 +8792,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8345,7 +8825,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -8370,7 +8850,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8392,7 +8872,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8402,12 +8882,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8417,75 +8897,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -8501,12 +9005,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8531,14 +9035,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -8552,26 +9068,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -8585,7 +9101,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -8610,7 +9126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -8627,27 +9143,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -8657,75 +9173,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -8741,12 +9281,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8771,14 +9311,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -8796,7 +9336,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
         <v>41.2</v>
@@ -8805,13 +9345,13 @@
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
         <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -8825,7 +9365,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8867,12 +9407,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -8882,7 +9422,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8897,67 +9437,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr"/>
@@ -8981,12 +9521,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9011,14 +9551,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>30.3</v>
+        <v>28.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9032,26 +9584,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9065,7 +9617,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9090,7 +9642,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9107,12 +9659,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9122,12 +9674,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9137,75 +9689,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9221,24 +9797,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9251,14 +9827,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>29.9</v>
+        <v>26.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9272,26 +9860,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9305,7 +9893,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9330,7 +9918,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9347,12 +9935,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9362,12 +9950,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -9377,75 +9965,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -9494,11 +10106,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -9519,7 +10143,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>17.3</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -9570,7 +10194,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -9607,7 +10231,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -9680,12 +10304,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-28_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -768,11 +768,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -786,65 +798,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
         <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +889,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -954,14 +962,46 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -975,24 +1015,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1000,19 +1040,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,65 +1078,61 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1101,12 +1149,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1116,92 +1164,124 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1215,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1240,22 +1320,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1264,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1278,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>61.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>37.8</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1353,12 +1429,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1368,116 +1444,124 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1491,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1516,19 +1600,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1542,65 +1638,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1617,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1632,12 +1724,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1647,77 +1739,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1731,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1756,22 +1880,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1780,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.7</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1794,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1869,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1899,101 +2019,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2032,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2040,11 +2168,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>47.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2058,65 +2198,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
         <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
         <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2153,7 +2289,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2198,12 +2334,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2226,14 +2362,46 @@
           <t>0.1565</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2247,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2272,19 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.2</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2298,65 +2478,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2373,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2403,12 +2579,12 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2418,62 +2594,94 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2512,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2520,11 +2728,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2538,65 +2758,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
         <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2633,7 +2849,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2683,7 +2899,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2706,14 +2922,46 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2732,7 +2980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2752,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2776,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.1</v>
+        <v>42.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2790,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2800,10 +3048,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -2813,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2935,7 +3179,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -2988,8 +3232,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3028,12 +3280,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.8</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3066,20 +3318,20 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3089,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3206,12 +3454,12 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -3264,8 +3512,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3279,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3304,19 +3560,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>32.5</v>
+        <v>34.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3330,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3410,7 +3674,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3420,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3435,77 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3519,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3544,19 +3840,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>32.1</v>
+        <v>34.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3570,65 +3878,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3645,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3675,77 +3979,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3759,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3784,22 +4120,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3808,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3822,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3897,12 +4229,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3912,12 +4244,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3927,101 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4035,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4060,22 +4400,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4084,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4098,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4173,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4203,101 +4539,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4311,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4336,19 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4362,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4437,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4452,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4467,77 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4551,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4576,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4600,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4614,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
         <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4689,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4704,7 +5084,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -4719,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -4812,8 +5192,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4827,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4852,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4876,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.7</v>
+        <v>28</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4890,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q18" t="n">
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4965,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4980,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -4995,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5088,8 +5472,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5128,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5152,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>26.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5166,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5176,10 +5568,10 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5189,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5364,8 +5752,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5730,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5738,11 +6134,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5756,65 +6164,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
         <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6255,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5924,14 +6328,46 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5945,24 +6381,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5970,19 +6406,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5996,65 +6444,61 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6071,12 +6515,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6086,92 +6530,124 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6185,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6210,22 +6686,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6234,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6248,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>61.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>37.8</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6323,12 +6795,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6338,116 +6810,124 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6461,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6486,19 +6966,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6512,65 +7004,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6587,12 +7075,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -6602,12 +7090,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6617,77 +7105,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6701,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6726,22 +7246,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6750,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.7</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6764,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6839,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6869,101 +7385,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7002,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7010,11 +7534,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>47.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7028,65 +7564,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
         <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
         <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7123,7 +7655,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7168,12 +7700,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -7196,14 +7728,46 @@
           <t>0.1565</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7217,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7242,19 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.2</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7268,65 +7844,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7343,27 +7915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7373,12 +7945,12 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -7388,62 +7960,94 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7482,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -7490,11 +8094,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7508,65 +8124,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
         <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -7603,7 +8215,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -7653,7 +8265,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -7676,14 +8288,46 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7702,7 +8346,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7722,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -7746,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.1</v>
+        <v>42.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7760,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -7770,10 +8414,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -7783,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7905,7 +8545,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -7958,8 +8598,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7998,12 +8646,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8022,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.8</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8036,20 +8684,20 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -8059,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8176,12 +8820,12 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -8234,8 +8878,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8249,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8274,19 +8926,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>32.5</v>
+        <v>34.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8300,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8380,7 +9040,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8390,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8405,77 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8489,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8514,19 +9206,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>32.1</v>
+        <v>34.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8540,65 +9244,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8615,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8645,77 +9345,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8729,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8754,22 +9486,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -8778,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8792,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8867,12 +9595,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8882,12 +9610,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8897,101 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9005,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9030,22 +9766,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9054,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9068,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9143,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9173,101 +9905,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9281,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9306,19 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9332,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -9407,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -9422,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9437,77 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9521,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9546,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9570,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9584,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
         <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9659,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9674,7 +10450,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -9689,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9782,8 +10558,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9797,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9822,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9846,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.7</v>
+        <v>28</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9860,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q18" t="n">
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9935,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9950,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -9965,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10058,8 +10838,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10098,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10122,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>26.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10136,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10146,10 +10934,10 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10159,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10334,8 +11118,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
